--- a/public/templates/master_template_custom - Copy.xlsx
+++ b/public/templates/master_template_custom - Copy.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B8D50CE-4FA8-4A5E-A023-0030E2B248E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97FC26B3-ABCB-407E-ADC3-9BD50CD5438B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="cover" sheetId="15" r:id="rId1"/>
@@ -34,7 +34,7 @@
     <definedName name="_2__123Graph_XCHART_1" hidden="1">[3]RAB!#REF!</definedName>
     <definedName name="_Fill" hidden="1">#REF!</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">ahsp!$A:$O</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">cover!$A$1:$I$44</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">cover!$A$1:$N$65</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'harga satuan'!$A1:$J2646</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">hsp!$A:$I</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="10">'laporan bulanan'!$A:$Q</definedName>
@@ -2365,15 +2365,6 @@
       <alignment vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2384,6 +2375,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2406,220 +2406,6 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="25" fillId="0" borderId="19" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="25" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="19" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="17" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="20" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="22" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="26" fillId="0" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="26" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="26" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="24" fillId="0" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="24" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="24" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="25" fillId="0" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="25" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="25" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="18" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="68" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="69" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="60" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="70" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="60" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="69" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="70" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="73" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="72" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="74" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="57" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="58" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="59" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="62" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="67" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="166" fontId="25" fillId="0" borderId="60" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="25" fillId="0" borderId="69" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="25" fillId="0" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="55" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="76" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="56" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="23" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="43" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="23" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="23" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="44" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="45" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="47" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="46" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="48" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="6" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="6" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="6" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="77" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2680,6 +2466,220 @@
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="17" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="18" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="62" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="67" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="25" fillId="0" borderId="60" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="25" fillId="0" borderId="69" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="25" fillId="0" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="55" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="76" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="56" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="22" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="23" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="43" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="23" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="23" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="44" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="45" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="47" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="46" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="48" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="19" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="20" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="26" fillId="0" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="26" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="26" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="24" fillId="0" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="24" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="24" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="25" fillId="0" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="25" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="25" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="25" fillId="0" borderId="19" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="25" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="68" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="69" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="60" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="70" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="60" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="69" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="70" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="73" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="72" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="74" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="57" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="58" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="59" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -2992,15 +2992,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:colOff>207818</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>25400</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>7620</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>581891</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>166254</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3029,8 +3029,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="5511800" cy="8054340"/>
+          <a:off x="207818" y="0"/>
+          <a:ext cx="8298873" cy="11693236"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3041,12 +3041,12 @@
   </xdr:twoCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>495300</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>47913</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>523010</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>12005</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="3611880" cy="487313"/>
+    <xdr:ext cx="3611880" cy="559127"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="5" name="TextBox 4">
@@ -3060,8 +3060,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1714500" y="4802793"/>
-          <a:ext cx="3611880" cy="487313"/>
+          <a:off x="4790210" y="7036260"/>
+          <a:ext cx="3611880" cy="559127"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3090,7 +3090,7 @@
         <a:p>
           <a:pPr algn="r"/>
           <a:r>
-            <a:rPr lang="en-ID" sz="2200">
+            <a:rPr lang="en-ID" sz="2600">
               <a:solidFill>
                 <a:schemeClr val="accent2"/>
               </a:solidFill>
@@ -3106,12 +3106,12 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>563880</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>175260</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>356061</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>64423</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="4244340" cy="269369"/>
+    <xdr:ext cx="4244340" cy="343043"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="6" name="TextBox 5">
@@ -3125,8 +3125,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1173480" y="2735580"/>
-          <a:ext cx="4244340" cy="269369"/>
+          <a:off x="2184861" y="3846714"/>
+          <a:ext cx="4244340" cy="343043"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3155,7 +3155,7 @@
         <a:p>
           <a:pPr algn="l"/>
           <a:r>
-            <a:rPr lang="en-ID" sz="1200">
+            <a:rPr lang="en-ID" sz="1700">
               <a:solidFill>
                 <a:schemeClr val="bg1"/>
               </a:solidFill>
@@ -3166,7 +3166,7 @@
             <a:t>&lt;NOMOR</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-ID" sz="1200" baseline="0">
+            <a:rPr lang="en-ID" sz="1700" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="bg1"/>
               </a:solidFill>
@@ -3177,7 +3177,7 @@
             <a:t> KONTRAK</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-ID" sz="1200">
+            <a:rPr lang="en-ID" sz="1700">
               <a:solidFill>
                 <a:schemeClr val="bg1"/>
               </a:solidFill>
@@ -3194,12 +3194,12 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>243840</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>105293</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>114299</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="3886200" cy="307777"/>
+    <xdr:ext cx="3886200" cy="397545"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="7" name="TextBox 6">
@@ -3213,8 +3213,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1463040" y="3040380"/>
-          <a:ext cx="3886200" cy="307777"/>
+          <a:off x="2543693" y="4256808"/>
+          <a:ext cx="3886200" cy="397545"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3243,7 +3243,7 @@
         <a:p>
           <a:pPr algn="l"/>
           <a:r>
-            <a:rPr lang="en-ID" sz="1200">
+            <a:rPr lang="en-ID" sz="1700">
               <a:solidFill>
                 <a:schemeClr val="bg1"/>
               </a:solidFill>
@@ -3259,10 +3259,10 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>541020</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>471746</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>34636</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="3596640" cy="739140"/>
     <xdr:sp macro="" textlink="">
@@ -3278,7 +3278,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1760220" y="3368040"/>
+          <a:off x="2910146" y="4717472"/>
           <a:ext cx="3596640" cy="739140"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3308,7 +3308,7 @@
         <a:p>
           <a:pPr algn="l"/>
           <a:r>
-            <a:rPr lang="en-ID" sz="1200">
+            <a:rPr lang="en-ID" sz="1700">
               <a:solidFill>
                 <a:schemeClr val="bg1"/>
               </a:solidFill>
@@ -3325,11 +3325,11 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>121920</xdr:rowOff>
+      <xdr:colOff>429491</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>94209</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="4244340" cy="269369"/>
+    <xdr:ext cx="4244340" cy="343043"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="9" name="TextBox 8">
@@ -3343,8 +3343,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="670560"/>
-          <a:ext cx="4244340" cy="269369"/>
+          <a:off x="429491" y="994754"/>
+          <a:ext cx="4244340" cy="343043"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3373,7 +3373,7 @@
         <a:p>
           <a:pPr algn="l"/>
           <a:r>
-            <a:rPr lang="en-ID" sz="1200">
+            <a:rPr lang="en-ID" sz="1700">
               <a:solidFill>
                 <a:schemeClr val="bg1"/>
               </a:solidFill>
@@ -3390,16 +3390,16 @@
   </xdr:oneCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>15240</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>263236</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>124691</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>579120</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>68580</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>412866</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>27017</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3414,8 +3414,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2133600" y="5318760"/>
-          <a:ext cx="3322320" cy="53340"/>
+          <a:off x="5140036" y="7509164"/>
+          <a:ext cx="3197630" cy="82435"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3960,11 +3960,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B97B6B6-7C65-4193-8D4E-4DE87F8A1BF2}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
+  <pageSetup paperSize="9" scale="82" fitToHeight="0" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
@@ -3998,40 +4001,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:16" ht="111.6" customHeight="1">
-      <c r="B1" s="179"/>
-      <c r="C1" s="179"/>
-      <c r="D1" s="179"/>
-      <c r="E1" s="179"/>
-      <c r="F1" s="179"/>
-      <c r="G1" s="179"/>
-      <c r="H1" s="179"/>
-      <c r="I1" s="179"/>
-      <c r="J1" s="179"/>
-      <c r="K1" s="179"/>
-      <c r="L1" s="179"/>
-      <c r="M1" s="179"/>
-      <c r="N1" s="179"/>
-      <c r="O1" s="179"/>
-      <c r="P1" s="179"/>
+      <c r="B1" s="176"/>
+      <c r="C1" s="176"/>
+      <c r="D1" s="176"/>
+      <c r="E1" s="176"/>
+      <c r="F1" s="176"/>
+      <c r="G1" s="176"/>
+      <c r="H1" s="176"/>
+      <c r="I1" s="176"/>
+      <c r="J1" s="176"/>
+      <c r="K1" s="176"/>
+      <c r="L1" s="176"/>
+      <c r="M1" s="176"/>
+      <c r="N1" s="176"/>
+      <c r="O1" s="176"/>
+      <c r="P1" s="176"/>
     </row>
     <row r="2" spans="2:16" ht="22.95" customHeight="1">
-      <c r="B2" s="180" t="s">
+      <c r="B2" s="177" t="s">
         <v>142</v>
       </c>
-      <c r="C2" s="181"/>
-      <c r="D2" s="181"/>
-      <c r="E2" s="181"/>
-      <c r="F2" s="181"/>
-      <c r="G2" s="181"/>
-      <c r="H2" s="181"/>
-      <c r="I2" s="181"/>
-      <c r="J2" s="181"/>
-      <c r="K2" s="181"/>
-      <c r="L2" s="181"/>
-      <c r="M2" s="181"/>
-      <c r="N2" s="181"/>
-      <c r="O2" s="181"/>
-      <c r="P2" s="181"/>
+      <c r="C2" s="178"/>
+      <c r="D2" s="178"/>
+      <c r="E2" s="178"/>
+      <c r="F2" s="178"/>
+      <c r="G2" s="178"/>
+      <c r="H2" s="178"/>
+      <c r="I2" s="178"/>
+      <c r="J2" s="178"/>
+      <c r="K2" s="178"/>
+      <c r="L2" s="178"/>
+      <c r="M2" s="178"/>
+      <c r="N2" s="178"/>
+      <c r="O2" s="178"/>
+      <c r="P2" s="178"/>
     </row>
     <row r="3" spans="2:16" ht="4.95" customHeight="1">
       <c r="B3"/>
@@ -4058,16 +4061,16 @@
       <c r="F4"/>
       <c r="G4"/>
       <c r="H4"/>
-      <c r="I4" s="182" t="s">
+      <c r="I4" s="179" t="s">
         <v>86</v>
       </c>
-      <c r="J4" s="182"/>
-      <c r="K4" s="182"/>
-      <c r="L4" s="182"/>
-      <c r="M4" s="182"/>
-      <c r="N4" s="182"/>
-      <c r="O4" s="182"/>
-      <c r="P4" s="182"/>
+      <c r="J4" s="179"/>
+      <c r="K4" s="179"/>
+      <c r="L4" s="179"/>
+      <c r="M4" s="179"/>
+      <c r="N4" s="179"/>
+      <c r="O4" s="179"/>
+      <c r="P4" s="179"/>
     </row>
     <row r="5" spans="2:16" ht="14.4" customHeight="1">
       <c r="B5" t="s">
@@ -4081,14 +4084,14 @@
       <c r="F5" s="56"/>
       <c r="G5" s="56"/>
       <c r="H5" s="56"/>
-      <c r="I5" s="182"/>
-      <c r="J5" s="182"/>
-      <c r="K5" s="182"/>
-      <c r="L5" s="182"/>
-      <c r="M5" s="182"/>
-      <c r="N5" s="182"/>
-      <c r="O5" s="182"/>
-      <c r="P5" s="182"/>
+      <c r="I5" s="179"/>
+      <c r="J5" s="179"/>
+      <c r="K5" s="179"/>
+      <c r="L5" s="179"/>
+      <c r="M5" s="179"/>
+      <c r="N5" s="179"/>
+      <c r="O5" s="179"/>
+      <c r="P5" s="179"/>
     </row>
     <row r="6" spans="2:16" ht="14.4" customHeight="1">
       <c r="B6" t="s">
@@ -4223,70 +4226,70 @@
       <c r="P11"/>
     </row>
     <row r="12" spans="2:16" s="62" customFormat="1" ht="14.4" customHeight="1">
-      <c r="B12" s="178" t="s">
+      <c r="B12" s="180" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="178" t="s">
+      <c r="C12" s="180" t="s">
         <v>76</v>
       </c>
-      <c r="D12" s="178"/>
-      <c r="E12" s="178"/>
-      <c r="F12" s="178" t="s">
+      <c r="D12" s="180"/>
+      <c r="E12" s="180"/>
+      <c r="F12" s="180" t="s">
         <v>148</v>
       </c>
-      <c r="G12" s="178" t="s">
+      <c r="G12" s="180" t="s">
         <v>150</v>
       </c>
-      <c r="H12" s="178" t="s">
+      <c r="H12" s="180" t="s">
         <v>149</v>
       </c>
-      <c r="I12" s="178" t="s">
+      <c r="I12" s="180" t="s">
         <v>151</v>
       </c>
-      <c r="J12" s="178" t="s">
+      <c r="J12" s="180" t="s">
         <v>155</v>
       </c>
-      <c r="K12" s="178"/>
-      <c r="L12" s="178"/>
-      <c r="M12" s="178"/>
-      <c r="N12" s="178"/>
-      <c r="O12" s="178"/>
-      <c r="P12" s="176" t="s">
+      <c r="K12" s="180"/>
+      <c r="L12" s="180"/>
+      <c r="M12" s="180"/>
+      <c r="N12" s="180"/>
+      <c r="O12" s="180"/>
+      <c r="P12" s="181" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="13" spans="2:16" s="61" customFormat="1">
-      <c r="B13" s="178"/>
-      <c r="C13" s="178"/>
-      <c r="D13" s="178"/>
-      <c r="E13" s="178"/>
-      <c r="F13" s="178"/>
-      <c r="G13" s="178"/>
-      <c r="H13" s="178"/>
-      <c r="I13" s="178"/>
-      <c r="J13" s="177" t="s">
+      <c r="B13" s="180"/>
+      <c r="C13" s="180"/>
+      <c r="D13" s="180"/>
+      <c r="E13" s="180"/>
+      <c r="F13" s="180"/>
+      <c r="G13" s="180"/>
+      <c r="H13" s="180"/>
+      <c r="I13" s="180"/>
+      <c r="J13" s="182" t="s">
         <v>152</v>
       </c>
-      <c r="K13" s="177"/>
-      <c r="L13" s="177" t="s">
+      <c r="K13" s="182"/>
+      <c r="L13" s="182" t="s">
         <v>157</v>
       </c>
-      <c r="M13" s="177"/>
-      <c r="N13" s="177" t="s">
+      <c r="M13" s="182"/>
+      <c r="N13" s="182" t="s">
         <v>158</v>
       </c>
-      <c r="O13" s="177"/>
-      <c r="P13" s="176"/>
+      <c r="O13" s="182"/>
+      <c r="P13" s="181"/>
     </row>
     <row r="14" spans="2:16" s="61" customFormat="1" ht="14.4" customHeight="1">
-      <c r="B14" s="178"/>
-      <c r="C14" s="178"/>
-      <c r="D14" s="178"/>
-      <c r="E14" s="178"/>
-      <c r="F14" s="178"/>
-      <c r="G14" s="178"/>
-      <c r="H14" s="178"/>
-      <c r="I14" s="178"/>
+      <c r="B14" s="180"/>
+      <c r="C14" s="180"/>
+      <c r="D14" s="180"/>
+      <c r="E14" s="180"/>
+      <c r="F14" s="180"/>
+      <c r="G14" s="180"/>
+      <c r="H14" s="180"/>
+      <c r="I14" s="180"/>
       <c r="J14" s="38" t="s">
         <v>120</v>
       </c>
@@ -4305,7 +4308,7 @@
       <c r="O14" s="40" t="s">
         <v>121</v>
       </c>
-      <c r="P14" s="176"/>
+      <c r="P14" s="181"/>
     </row>
     <row r="15" spans="2:16">
       <c r="C15" s="59"/>
@@ -4693,40 +4696,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:16" ht="111.6" customHeight="1">
-      <c r="B1" s="179"/>
-      <c r="C1" s="179"/>
-      <c r="D1" s="179"/>
-      <c r="E1" s="179"/>
-      <c r="F1" s="179"/>
-      <c r="G1" s="179"/>
-      <c r="H1" s="179"/>
-      <c r="I1" s="179"/>
-      <c r="J1" s="179"/>
-      <c r="K1" s="179"/>
-      <c r="L1" s="179"/>
-      <c r="M1" s="179"/>
-      <c r="N1" s="179"/>
-      <c r="O1" s="179"/>
-      <c r="P1" s="179"/>
+      <c r="B1" s="176"/>
+      <c r="C1" s="176"/>
+      <c r="D1" s="176"/>
+      <c r="E1" s="176"/>
+      <c r="F1" s="176"/>
+      <c r="G1" s="176"/>
+      <c r="H1" s="176"/>
+      <c r="I1" s="176"/>
+      <c r="J1" s="176"/>
+      <c r="K1" s="176"/>
+      <c r="L1" s="176"/>
+      <c r="M1" s="176"/>
+      <c r="N1" s="176"/>
+      <c r="O1" s="176"/>
+      <c r="P1" s="176"/>
     </row>
     <row r="2" spans="2:16" ht="22.95" customHeight="1">
-      <c r="B2" s="180" t="s">
+      <c r="B2" s="177" t="s">
         <v>161</v>
       </c>
-      <c r="C2" s="181"/>
-      <c r="D2" s="181"/>
-      <c r="E2" s="181"/>
-      <c r="F2" s="181"/>
-      <c r="G2" s="181"/>
-      <c r="H2" s="181"/>
-      <c r="I2" s="181"/>
-      <c r="J2" s="181"/>
-      <c r="K2" s="181"/>
-      <c r="L2" s="181"/>
-      <c r="M2" s="181"/>
-      <c r="N2" s="181"/>
-      <c r="O2" s="181"/>
-      <c r="P2" s="181"/>
+      <c r="C2" s="178"/>
+      <c r="D2" s="178"/>
+      <c r="E2" s="178"/>
+      <c r="F2" s="178"/>
+      <c r="G2" s="178"/>
+      <c r="H2" s="178"/>
+      <c r="I2" s="178"/>
+      <c r="J2" s="178"/>
+      <c r="K2" s="178"/>
+      <c r="L2" s="178"/>
+      <c r="M2" s="178"/>
+      <c r="N2" s="178"/>
+      <c r="O2" s="178"/>
+      <c r="P2" s="178"/>
     </row>
     <row r="3" spans="2:16" ht="4.95" customHeight="1">
       <c r="B3"/>
@@ -4753,16 +4756,16 @@
       <c r="F4" s="61"/>
       <c r="G4"/>
       <c r="H4"/>
-      <c r="I4" s="182" t="s">
+      <c r="I4" s="179" t="s">
         <v>86</v>
       </c>
-      <c r="J4" s="182"/>
-      <c r="K4" s="182"/>
-      <c r="L4" s="182"/>
-      <c r="M4" s="182"/>
-      <c r="N4" s="182"/>
-      <c r="O4" s="182"/>
-      <c r="P4" s="182"/>
+      <c r="J4" s="179"/>
+      <c r="K4" s="179"/>
+      <c r="L4" s="179"/>
+      <c r="M4" s="179"/>
+      <c r="N4" s="179"/>
+      <c r="O4" s="179"/>
+      <c r="P4" s="179"/>
     </row>
     <row r="5" spans="2:16" ht="14.4" customHeight="1">
       <c r="B5" t="s">
@@ -4776,14 +4779,14 @@
       <c r="F5" s="58"/>
       <c r="G5" s="56"/>
       <c r="H5" s="56"/>
-      <c r="I5" s="182"/>
-      <c r="J5" s="182"/>
-      <c r="K5" s="182"/>
-      <c r="L5" s="182"/>
-      <c r="M5" s="182"/>
-      <c r="N5" s="182"/>
-      <c r="O5" s="182"/>
-      <c r="P5" s="182"/>
+      <c r="I5" s="179"/>
+      <c r="J5" s="179"/>
+      <c r="K5" s="179"/>
+      <c r="L5" s="179"/>
+      <c r="M5" s="179"/>
+      <c r="N5" s="179"/>
+      <c r="O5" s="179"/>
+      <c r="P5" s="179"/>
     </row>
     <row r="6" spans="2:16" ht="14.4" customHeight="1">
       <c r="B6" t="s">
@@ -4918,70 +4921,70 @@
       <c r="P11"/>
     </row>
     <row r="12" spans="2:16" s="62" customFormat="1" ht="14.4" customHeight="1">
-      <c r="B12" s="178" t="s">
+      <c r="B12" s="180" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="178" t="s">
+      <c r="C12" s="180" t="s">
         <v>76</v>
       </c>
-      <c r="D12" s="178"/>
-      <c r="E12" s="178"/>
-      <c r="F12" s="178" t="s">
+      <c r="D12" s="180"/>
+      <c r="E12" s="180"/>
+      <c r="F12" s="180" t="s">
         <v>148</v>
       </c>
-      <c r="G12" s="178" t="s">
+      <c r="G12" s="180" t="s">
         <v>150</v>
       </c>
-      <c r="H12" s="178" t="s">
+      <c r="H12" s="180" t="s">
         <v>149</v>
       </c>
-      <c r="I12" s="178" t="s">
+      <c r="I12" s="180" t="s">
         <v>151</v>
       </c>
-      <c r="J12" s="178" t="s">
+      <c r="J12" s="180" t="s">
         <v>155</v>
       </c>
-      <c r="K12" s="178"/>
-      <c r="L12" s="178"/>
-      <c r="M12" s="178"/>
-      <c r="N12" s="178"/>
-      <c r="O12" s="178"/>
-      <c r="P12" s="176" t="s">
+      <c r="K12" s="180"/>
+      <c r="L12" s="180"/>
+      <c r="M12" s="180"/>
+      <c r="N12" s="180"/>
+      <c r="O12" s="180"/>
+      <c r="P12" s="181" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="13" spans="2:16" s="61" customFormat="1">
-      <c r="B13" s="178"/>
-      <c r="C13" s="178"/>
-      <c r="D13" s="178"/>
-      <c r="E13" s="178"/>
-      <c r="F13" s="178"/>
-      <c r="G13" s="178"/>
-      <c r="H13" s="178"/>
-      <c r="I13" s="178"/>
-      <c r="J13" s="177" t="s">
+      <c r="B13" s="180"/>
+      <c r="C13" s="180"/>
+      <c r="D13" s="180"/>
+      <c r="E13" s="180"/>
+      <c r="F13" s="180"/>
+      <c r="G13" s="180"/>
+      <c r="H13" s="180"/>
+      <c r="I13" s="180"/>
+      <c r="J13" s="182" t="s">
         <v>152</v>
       </c>
-      <c r="K13" s="177"/>
-      <c r="L13" s="177" t="s">
+      <c r="K13" s="182"/>
+      <c r="L13" s="182" t="s">
         <v>153</v>
       </c>
-      <c r="M13" s="177"/>
-      <c r="N13" s="177" t="s">
+      <c r="M13" s="182"/>
+      <c r="N13" s="182" t="s">
         <v>154</v>
       </c>
-      <c r="O13" s="177"/>
-      <c r="P13" s="176"/>
+      <c r="O13" s="182"/>
+      <c r="P13" s="181"/>
     </row>
     <row r="14" spans="2:16" s="61" customFormat="1" ht="14.4" customHeight="1">
-      <c r="B14" s="178"/>
-      <c r="C14" s="178"/>
-      <c r="D14" s="178"/>
-      <c r="E14" s="178"/>
-      <c r="F14" s="178"/>
-      <c r="G14" s="178"/>
-      <c r="H14" s="178"/>
-      <c r="I14" s="178"/>
+      <c r="B14" s="180"/>
+      <c r="C14" s="180"/>
+      <c r="D14" s="180"/>
+      <c r="E14" s="180"/>
+      <c r="F14" s="180"/>
+      <c r="G14" s="180"/>
+      <c r="H14" s="180"/>
+      <c r="I14" s="180"/>
       <c r="J14" s="38" t="s">
         <v>120</v>
       </c>
@@ -5000,7 +5003,7 @@
       <c r="O14" s="40" t="s">
         <v>121</v>
       </c>
-      <c r="P14" s="176"/>
+      <c r="P14" s="181"/>
     </row>
     <row r="15" spans="2:16">
       <c r="C15" s="59"/>
@@ -13906,10 +13909,10 @@
       <c r="B5" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="178" t="s">
+      <c r="C5" s="180" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="178"/>
+      <c r="D5" s="180"/>
       <c r="E5" s="38" t="s">
         <v>8</v>
       </c>
@@ -40232,30 +40235,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:11" ht="111.6" customHeight="1">
-      <c r="B1" s="179"/>
-      <c r="C1" s="179"/>
-      <c r="D1" s="179"/>
-      <c r="E1" s="179"/>
-      <c r="F1" s="179"/>
-      <c r="G1" s="179"/>
-      <c r="H1" s="179"/>
-      <c r="I1" s="179"/>
-      <c r="J1" s="179"/>
-      <c r="K1" s="179"/>
+      <c r="B1" s="176"/>
+      <c r="C1" s="176"/>
+      <c r="D1" s="176"/>
+      <c r="E1" s="176"/>
+      <c r="F1" s="176"/>
+      <c r="G1" s="176"/>
+      <c r="H1" s="176"/>
+      <c r="I1" s="176"/>
+      <c r="J1" s="176"/>
+      <c r="K1" s="176"/>
     </row>
     <row r="2" spans="2:11" ht="22.95" customHeight="1">
-      <c r="B2" s="180" t="s">
+      <c r="B2" s="177" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="181"/>
-      <c r="D2" s="181"/>
-      <c r="E2" s="181"/>
-      <c r="F2" s="181"/>
-      <c r="G2" s="181"/>
-      <c r="H2" s="181"/>
-      <c r="I2" s="181"/>
-      <c r="J2" s="181"/>
-      <c r="K2" s="181"/>
+      <c r="C2" s="178"/>
+      <c r="D2" s="178"/>
+      <c r="E2" s="178"/>
+      <c r="F2" s="178"/>
+      <c r="G2" s="178"/>
+      <c r="H2" s="178"/>
+      <c r="I2" s="178"/>
+      <c r="J2" s="178"/>
+      <c r="K2" s="178"/>
     </row>
     <row r="3" spans="2:11" ht="4.95" customHeight="1">
       <c r="B3"/>
@@ -40375,11 +40378,11 @@
       <c r="B11" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="178" t="s">
+      <c r="C11" s="180" t="s">
         <v>76</v>
       </c>
-      <c r="D11" s="178"/>
-      <c r="E11" s="178"/>
+      <c r="D11" s="180"/>
+      <c r="E11" s="180"/>
       <c r="F11" s="38" t="s">
         <v>26</v>
       </c>
@@ -41808,24 +41811,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:8" ht="111.6" customHeight="1">
-      <c r="B1" s="179"/>
-      <c r="C1" s="179"/>
-      <c r="D1" s="179"/>
-      <c r="E1" s="179"/>
-      <c r="F1" s="179"/>
-      <c r="G1" s="179"/>
-      <c r="H1" s="179"/>
+      <c r="B1" s="176"/>
+      <c r="C1" s="176"/>
+      <c r="D1" s="176"/>
+      <c r="E1" s="176"/>
+      <c r="F1" s="176"/>
+      <c r="G1" s="176"/>
+      <c r="H1" s="176"/>
     </row>
     <row r="2" spans="2:8" ht="22.95" customHeight="1">
-      <c r="B2" s="180" t="s">
+      <c r="B2" s="177" t="s">
         <v>74</v>
       </c>
-      <c r="C2" s="181"/>
-      <c r="D2" s="181"/>
-      <c r="E2" s="181"/>
-      <c r="F2" s="181"/>
-      <c r="G2" s="181"/>
-      <c r="H2" s="181"/>
+      <c r="C2" s="178"/>
+      <c r="D2" s="178"/>
+      <c r="E2" s="178"/>
+      <c r="F2" s="178"/>
+      <c r="G2" s="178"/>
+      <c r="H2" s="178"/>
     </row>
     <row r="3" spans="2:8" ht="4.95" customHeight="1">
       <c r="B3"/>
@@ -41927,11 +41930,11 @@
       <c r="B11" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="178" t="s">
+      <c r="C11" s="180" t="s">
         <v>76</v>
       </c>
-      <c r="D11" s="178"/>
-      <c r="E11" s="178"/>
+      <c r="D11" s="180"/>
+      <c r="E11" s="180"/>
       <c r="F11" s="40" t="s">
         <v>29</v>
       </c>
@@ -43161,11 +43164,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="100.05" customHeight="1">
-      <c r="B1" s="179"/>
-      <c r="C1" s="179"/>
-      <c r="D1" s="179"/>
-      <c r="E1" s="179"/>
-      <c r="F1" s="179"/>
+      <c r="B1" s="176"/>
+      <c r="C1" s="176"/>
+      <c r="D1" s="176"/>
+      <c r="E1" s="176"/>
+      <c r="F1" s="176"/>
     </row>
     <row r="2" spans="2:12" ht="18">
       <c r="B2" s="189" t="s">
@@ -43177,11 +43180,11 @@
       <c r="F2" s="189"/>
     </row>
     <row r="3" spans="2:12">
-      <c r="B3" s="179"/>
-      <c r="C3" s="179"/>
-      <c r="D3" s="179"/>
-      <c r="E3" s="179"/>
-      <c r="F3" s="179"/>
+      <c r="B3" s="176"/>
+      <c r="C3" s="176"/>
+      <c r="D3" s="176"/>
+      <c r="E3" s="176"/>
+      <c r="F3" s="176"/>
     </row>
     <row r="5" spans="2:12" s="58" customFormat="1">
       <c r="B5" s="187" t="s">
@@ -43343,50 +43346,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="88.8" customHeight="1" thickTop="1" thickBot="1">
-      <c r="B1" s="253"/>
-      <c r="C1" s="254"/>
-      <c r="D1" s="254"/>
-      <c r="E1" s="254"/>
-      <c r="F1" s="254"/>
-      <c r="G1" s="254"/>
-      <c r="H1" s="254"/>
-      <c r="I1" s="254"/>
-      <c r="J1" s="254"/>
-      <c r="K1" s="254"/>
-      <c r="L1" s="254"/>
-      <c r="M1" s="255"/>
+      <c r="B1" s="190"/>
+      <c r="C1" s="191"/>
+      <c r="D1" s="191"/>
+      <c r="E1" s="191"/>
+      <c r="F1" s="191"/>
+      <c r="G1" s="191"/>
+      <c r="H1" s="191"/>
+      <c r="I1" s="191"/>
+      <c r="J1" s="191"/>
+      <c r="K1" s="191"/>
+      <c r="L1" s="191"/>
+      <c r="M1" s="192"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1" thickTop="1">
-      <c r="B2" s="256" t="s">
+      <c r="B2" s="193" t="s">
         <v>85</v>
       </c>
-      <c r="C2" s="257"/>
-      <c r="D2" s="257"/>
-      <c r="E2" s="257"/>
-      <c r="F2" s="257"/>
-      <c r="G2" s="257"/>
-      <c r="H2" s="257"/>
-      <c r="I2" s="258"/>
-      <c r="J2" s="262" t="s">
+      <c r="C2" s="194"/>
+      <c r="D2" s="194"/>
+      <c r="E2" s="194"/>
+      <c r="F2" s="194"/>
+      <c r="G2" s="194"/>
+      <c r="H2" s="194"/>
+      <c r="I2" s="195"/>
+      <c r="J2" s="199" t="s">
         <v>86</v>
       </c>
-      <c r="K2" s="263"/>
-      <c r="L2" s="263"/>
-      <c r="M2" s="264"/>
+      <c r="K2" s="200"/>
+      <c r="L2" s="200"/>
+      <c r="M2" s="201"/>
     </row>
     <row r="3" spans="1:14" ht="14.4" customHeight="1">
-      <c r="B3" s="259"/>
-      <c r="C3" s="260"/>
-      <c r="D3" s="260"/>
-      <c r="E3" s="260"/>
-      <c r="F3" s="260"/>
-      <c r="G3" s="260"/>
-      <c r="H3" s="260"/>
-      <c r="I3" s="261"/>
-      <c r="J3" s="265"/>
-      <c r="K3" s="266"/>
-      <c r="L3" s="266"/>
-      <c r="M3" s="267"/>
+      <c r="B3" s="196"/>
+      <c r="C3" s="197"/>
+      <c r="D3" s="197"/>
+      <c r="E3" s="197"/>
+      <c r="F3" s="197"/>
+      <c r="G3" s="197"/>
+      <c r="H3" s="197"/>
+      <c r="I3" s="198"/>
+      <c r="J3" s="202"/>
+      <c r="K3" s="203"/>
+      <c r="L3" s="203"/>
+      <c r="M3" s="204"/>
     </row>
     <row r="4" spans="1:14" ht="14.4" customHeight="1">
       <c r="B4" s="77"/>
@@ -43397,10 +43400,10 @@
       <c r="G4" s="78"/>
       <c r="H4" s="78"/>
       <c r="I4" s="78"/>
-      <c r="J4" s="265"/>
-      <c r="K4" s="266"/>
-      <c r="L4" s="266"/>
-      <c r="M4" s="267"/>
+      <c r="J4" s="202"/>
+      <c r="K4" s="203"/>
+      <c r="L4" s="203"/>
+      <c r="M4" s="204"/>
     </row>
     <row r="5" spans="1:14" ht="15.6" customHeight="1">
       <c r="B5" s="79" t="s">
@@ -43417,10 +43420,10 @@
       <c r="G5" s="81"/>
       <c r="H5" s="81"/>
       <c r="I5" s="82"/>
-      <c r="J5" s="265"/>
-      <c r="K5" s="266"/>
-      <c r="L5" s="266"/>
-      <c r="M5" s="267"/>
+      <c r="J5" s="202"/>
+      <c r="K5" s="203"/>
+      <c r="L5" s="203"/>
+      <c r="M5" s="204"/>
     </row>
     <row r="6" spans="1:14" ht="15.6" customHeight="1">
       <c r="B6" s="79" t="s">
@@ -43437,10 +43440,10 @@
       <c r="G6" s="80"/>
       <c r="H6" s="80"/>
       <c r="I6" s="83"/>
-      <c r="J6" s="268"/>
-      <c r="K6" s="269"/>
-      <c r="L6" s="269"/>
-      <c r="M6" s="270"/>
+      <c r="J6" s="205"/>
+      <c r="K6" s="206"/>
+      <c r="L6" s="206"/>
+      <c r="M6" s="207"/>
     </row>
     <row r="7" spans="1:14" ht="15.6">
       <c r="B7" s="79" t="s">
@@ -43515,52 +43518,52 @@
       <c r="M9" s="89"/>
     </row>
     <row r="10" spans="1:14" ht="15.6">
-      <c r="B10" s="213" t="s">
+      <c r="B10" s="208" t="s">
         <v>94</v>
       </c>
-      <c r="C10" s="200"/>
-      <c r="D10" s="200"/>
-      <c r="E10" s="200"/>
-      <c r="F10" s="200"/>
-      <c r="G10" s="200" t="s">
+      <c r="C10" s="209"/>
+      <c r="D10" s="209"/>
+      <c r="E10" s="209"/>
+      <c r="F10" s="209"/>
+      <c r="G10" s="209" t="s">
         <v>95</v>
       </c>
-      <c r="H10" s="200"/>
-      <c r="I10" s="200"/>
-      <c r="J10" s="214"/>
-      <c r="K10" s="199" t="s">
+      <c r="H10" s="209"/>
+      <c r="I10" s="209"/>
+      <c r="J10" s="210"/>
+      <c r="K10" s="234" t="s">
         <v>96</v>
       </c>
-      <c r="L10" s="200"/>
-      <c r="M10" s="201"/>
+      <c r="L10" s="209"/>
+      <c r="M10" s="235"/>
     </row>
     <row r="11" spans="1:14" ht="16.2" thickBot="1">
       <c r="A11" s="58"/>
       <c r="B11" s="91" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="202" t="s">
+      <c r="C11" s="220" t="s">
         <v>97</v>
       </c>
-      <c r="D11" s="241"/>
-      <c r="E11" s="241"/>
+      <c r="D11" s="221"/>
+      <c r="E11" s="221"/>
       <c r="F11" s="92" t="s">
         <v>98</v>
       </c>
-      <c r="G11" s="202" t="s">
+      <c r="G11" s="220" t="s">
         <v>99</v>
       </c>
-      <c r="H11" s="203"/>
+      <c r="H11" s="222"/>
       <c r="I11" s="93" t="s">
         <v>27</v>
       </c>
       <c r="J11" s="92" t="s">
         <v>26</v>
       </c>
-      <c r="K11" s="202" t="s">
+      <c r="K11" s="220" t="s">
         <v>100</v>
       </c>
-      <c r="L11" s="203"/>
+      <c r="L11" s="222"/>
       <c r="M11" s="94" t="s">
         <v>101</v>
       </c>
@@ -43829,58 +43832,58 @@
       <c r="M22" s="123"/>
     </row>
     <row r="23" spans="1:13" ht="16.2" thickBot="1">
-      <c r="B23" s="242"/>
-      <c r="C23" s="243"/>
-      <c r="D23" s="243"/>
-      <c r="E23" s="243"/>
+      <c r="B23" s="223"/>
+      <c r="C23" s="224"/>
+      <c r="D23" s="224"/>
+      <c r="E23" s="224"/>
       <c r="F23" s="124"/>
       <c r="G23" s="124"/>
       <c r="H23" s="125"/>
       <c r="I23" s="125"/>
-      <c r="J23" s="244"/>
-      <c r="K23" s="244"/>
-      <c r="L23" s="244"/>
-      <c r="M23" s="245"/>
+      <c r="J23" s="225"/>
+      <c r="K23" s="225"/>
+      <c r="L23" s="225"/>
+      <c r="M23" s="226"/>
     </row>
     <row r="24" spans="1:13" ht="16.2" customHeight="1" thickTop="1">
       <c r="A24" s="160" t="s">
         <v>118</v>
       </c>
-      <c r="B24" s="246" t="s">
+      <c r="B24" s="227" t="s">
         <v>6</v>
       </c>
-      <c r="C24" s="248" t="s">
+      <c r="C24" s="229" t="s">
         <v>76</v>
       </c>
-      <c r="D24" s="248"/>
-      <c r="E24" s="248"/>
-      <c r="F24" s="248"/>
-      <c r="G24" s="248"/>
-      <c r="H24" s="248"/>
-      <c r="I24" s="248"/>
-      <c r="J24" s="250" t="s">
+      <c r="D24" s="229"/>
+      <c r="E24" s="229"/>
+      <c r="F24" s="229"/>
+      <c r="G24" s="229"/>
+      <c r="H24" s="229"/>
+      <c r="I24" s="229"/>
+      <c r="J24" s="231" t="s">
         <v>119</v>
       </c>
-      <c r="K24" s="251"/>
-      <c r="L24" s="251"/>
-      <c r="M24" s="252"/>
+      <c r="K24" s="232"/>
+      <c r="L24" s="232"/>
+      <c r="M24" s="233"/>
     </row>
     <row r="25" spans="1:13" ht="31.2">
-      <c r="B25" s="247"/>
-      <c r="C25" s="249"/>
-      <c r="D25" s="249"/>
-      <c r="E25" s="249"/>
-      <c r="F25" s="249"/>
-      <c r="G25" s="249"/>
-      <c r="H25" s="249"/>
-      <c r="I25" s="249"/>
+      <c r="B25" s="228"/>
+      <c r="C25" s="230"/>
+      <c r="D25" s="230"/>
+      <c r="E25" s="230"/>
+      <c r="F25" s="230"/>
+      <c r="G25" s="230"/>
+      <c r="H25" s="230"/>
+      <c r="I25" s="230"/>
       <c r="J25" s="90" t="s">
         <v>9</v>
       </c>
-      <c r="K25" s="193" t="s">
+      <c r="K25" s="248" t="s">
         <v>120</v>
       </c>
-      <c r="L25" s="194"/>
+      <c r="L25" s="249"/>
       <c r="M25" s="126" t="s">
         <v>121</v>
       </c>
@@ -44438,64 +44441,64 @@
       </c>
     </row>
     <row r="49" spans="2:13" ht="16.2" thickTop="1">
-      <c r="B49" s="226" t="s">
+      <c r="B49" s="265" t="s">
         <v>122</v>
       </c>
-      <c r="C49" s="227"/>
-      <c r="D49" s="227"/>
-      <c r="E49" s="227"/>
-      <c r="F49" s="227"/>
-      <c r="G49" s="227"/>
-      <c r="H49" s="227"/>
-      <c r="I49" s="227"/>
-      <c r="J49" s="228"/>
-      <c r="K49" s="238" t="s">
+      <c r="C49" s="266"/>
+      <c r="D49" s="266"/>
+      <c r="E49" s="266"/>
+      <c r="F49" s="266"/>
+      <c r="G49" s="266"/>
+      <c r="H49" s="266"/>
+      <c r="I49" s="266"/>
+      <c r="J49" s="267"/>
+      <c r="K49" s="217" t="s">
         <v>123</v>
       </c>
-      <c r="L49" s="239"/>
-      <c r="M49" s="240"/>
+      <c r="L49" s="218"/>
+      <c r="M49" s="219"/>
     </row>
     <row r="50" spans="2:13" ht="15.6" customHeight="1">
-      <c r="B50" s="229"/>
-      <c r="C50" s="230"/>
-      <c r="D50" s="230"/>
-      <c r="E50" s="230"/>
-      <c r="F50" s="230"/>
-      <c r="G50" s="230"/>
-      <c r="H50" s="230"/>
-      <c r="I50" s="230"/>
-      <c r="J50" s="231"/>
-      <c r="K50" s="235" t="s">
+      <c r="B50" s="268"/>
+      <c r="C50" s="269"/>
+      <c r="D50" s="269"/>
+      <c r="E50" s="269"/>
+      <c r="F50" s="269"/>
+      <c r="G50" s="269"/>
+      <c r="H50" s="269"/>
+      <c r="I50" s="269"/>
+      <c r="J50" s="270"/>
+      <c r="K50" s="214" t="s">
         <v>124</v>
       </c>
-      <c r="L50" s="236"/>
-      <c r="M50" s="237"/>
+      <c r="L50" s="215"/>
+      <c r="M50" s="216"/>
     </row>
     <row r="51" spans="2:13" ht="15.6">
       <c r="B51" s="138"/>
-      <c r="C51" s="232"/>
-      <c r="D51" s="232"/>
-      <c r="E51" s="232"/>
-      <c r="F51" s="232"/>
-      <c r="G51" s="232"/>
-      <c r="H51" s="232"/>
-      <c r="I51" s="232"/>
+      <c r="C51" s="211"/>
+      <c r="D51" s="211"/>
+      <c r="E51" s="211"/>
+      <c r="F51" s="211"/>
+      <c r="G51" s="211"/>
+      <c r="H51" s="211"/>
+      <c r="I51" s="211"/>
       <c r="J51" s="139"/>
-      <c r="K51" s="210" t="s">
+      <c r="K51" s="242" t="s">
         <v>86</v>
       </c>
-      <c r="L51" s="211"/>
-      <c r="M51" s="212"/>
+      <c r="L51" s="243"/>
+      <c r="M51" s="244"/>
     </row>
     <row r="52" spans="2:13" ht="15.6">
       <c r="B52" s="140"/>
-      <c r="C52" s="233"/>
-      <c r="D52" s="233"/>
-      <c r="E52" s="233"/>
-      <c r="F52" s="233"/>
-      <c r="G52" s="233"/>
-      <c r="H52" s="233"/>
-      <c r="I52" s="233"/>
+      <c r="C52" s="212"/>
+      <c r="D52" s="212"/>
+      <c r="E52" s="212"/>
+      <c r="F52" s="212"/>
+      <c r="G52" s="212"/>
+      <c r="H52" s="212"/>
+      <c r="I52" s="212"/>
       <c r="J52" s="141"/>
       <c r="K52" s="172"/>
       <c r="L52" s="169"/>
@@ -44503,13 +44506,13 @@
     </row>
     <row r="53" spans="2:13" ht="15.6">
       <c r="B53" s="140"/>
-      <c r="C53" s="233"/>
-      <c r="D53" s="233"/>
-      <c r="E53" s="233"/>
-      <c r="F53" s="233"/>
-      <c r="G53" s="233"/>
-      <c r="H53" s="233"/>
-      <c r="I53" s="233"/>
+      <c r="C53" s="212"/>
+      <c r="D53" s="212"/>
+      <c r="E53" s="212"/>
+      <c r="F53" s="212"/>
+      <c r="G53" s="212"/>
+      <c r="H53" s="212"/>
+      <c r="I53" s="212"/>
       <c r="J53" s="141"/>
       <c r="K53" s="172"/>
       <c r="L53" s="169"/>
@@ -44517,13 +44520,13 @@
     </row>
     <row r="54" spans="2:13" ht="15.6">
       <c r="B54" s="140"/>
-      <c r="C54" s="233"/>
-      <c r="D54" s="233"/>
-      <c r="E54" s="233"/>
-      <c r="F54" s="233"/>
-      <c r="G54" s="233"/>
-      <c r="H54" s="233"/>
-      <c r="I54" s="233"/>
+      <c r="C54" s="212"/>
+      <c r="D54" s="212"/>
+      <c r="E54" s="212"/>
+      <c r="F54" s="212"/>
+      <c r="G54" s="212"/>
+      <c r="H54" s="212"/>
+      <c r="I54" s="212"/>
       <c r="J54" s="141"/>
       <c r="K54" s="172"/>
       <c r="L54" s="169"/>
@@ -44531,13 +44534,13 @@
     </row>
     <row r="55" spans="2:13" ht="15.6">
       <c r="B55" s="143"/>
-      <c r="C55" s="233"/>
-      <c r="D55" s="233"/>
-      <c r="E55" s="233"/>
-      <c r="F55" s="233"/>
-      <c r="G55" s="233"/>
-      <c r="H55" s="233"/>
-      <c r="I55" s="233"/>
+      <c r="C55" s="212"/>
+      <c r="D55" s="212"/>
+      <c r="E55" s="212"/>
+      <c r="F55" s="212"/>
+      <c r="G55" s="212"/>
+      <c r="H55" s="212"/>
+      <c r="I55" s="212"/>
       <c r="J55" s="144"/>
       <c r="K55" s="172"/>
       <c r="L55" s="145"/>
@@ -44545,13 +44548,13 @@
     </row>
     <row r="56" spans="2:13" ht="15.6">
       <c r="B56" s="143"/>
-      <c r="C56" s="233"/>
-      <c r="D56" s="233"/>
-      <c r="E56" s="233"/>
-      <c r="F56" s="233"/>
-      <c r="G56" s="233"/>
-      <c r="H56" s="233"/>
-      <c r="I56" s="233"/>
+      <c r="C56" s="212"/>
+      <c r="D56" s="212"/>
+      <c r="E56" s="212"/>
+      <c r="F56" s="212"/>
+      <c r="G56" s="212"/>
+      <c r="H56" s="212"/>
+      <c r="I56" s="212"/>
       <c r="J56" s="144"/>
       <c r="K56" s="172"/>
       <c r="L56" s="145"/>
@@ -44559,45 +44562,45 @@
     </row>
     <row r="57" spans="2:13" ht="15.6">
       <c r="B57" s="143"/>
-      <c r="C57" s="233"/>
-      <c r="D57" s="233"/>
-      <c r="E57" s="233"/>
-      <c r="F57" s="233"/>
-      <c r="G57" s="233"/>
-      <c r="H57" s="233"/>
-      <c r="I57" s="233"/>
+      <c r="C57" s="212"/>
+      <c r="D57" s="212"/>
+      <c r="E57" s="212"/>
+      <c r="F57" s="212"/>
+      <c r="G57" s="212"/>
+      <c r="H57" s="212"/>
+      <c r="I57" s="212"/>
       <c r="J57" s="144"/>
-      <c r="K57" s="204" t="s">
+      <c r="K57" s="236" t="s">
         <v>125</v>
       </c>
-      <c r="L57" s="205"/>
-      <c r="M57" s="206"/>
+      <c r="L57" s="237"/>
+      <c r="M57" s="238"/>
     </row>
     <row r="58" spans="2:13" ht="15.6">
       <c r="B58" s="143"/>
-      <c r="C58" s="233"/>
-      <c r="D58" s="233"/>
-      <c r="E58" s="233"/>
-      <c r="F58" s="233"/>
-      <c r="G58" s="233"/>
-      <c r="H58" s="233"/>
-      <c r="I58" s="233"/>
+      <c r="C58" s="212"/>
+      <c r="D58" s="212"/>
+      <c r="E58" s="212"/>
+      <c r="F58" s="212"/>
+      <c r="G58" s="212"/>
+      <c r="H58" s="212"/>
+      <c r="I58" s="212"/>
       <c r="J58" s="144"/>
-      <c r="K58" s="207" t="s">
+      <c r="K58" s="239" t="s">
         <v>126</v>
       </c>
-      <c r="L58" s="208"/>
-      <c r="M58" s="209"/>
+      <c r="L58" s="240"/>
+      <c r="M58" s="241"/>
     </row>
     <row r="59" spans="2:13" ht="15.6">
       <c r="B59" s="143"/>
-      <c r="C59" s="233"/>
-      <c r="D59" s="233"/>
-      <c r="E59" s="233"/>
-      <c r="F59" s="233"/>
-      <c r="G59" s="233"/>
-      <c r="H59" s="233"/>
-      <c r="I59" s="233"/>
+      <c r="C59" s="212"/>
+      <c r="D59" s="212"/>
+      <c r="E59" s="212"/>
+      <c r="F59" s="212"/>
+      <c r="G59" s="212"/>
+      <c r="H59" s="212"/>
+      <c r="I59" s="212"/>
       <c r="J59" s="144"/>
       <c r="K59" s="172"/>
       <c r="L59" s="170"/>
@@ -44605,13 +44608,13 @@
     </row>
     <row r="60" spans="2:13" ht="15.6">
       <c r="B60" s="143"/>
-      <c r="C60" s="233"/>
-      <c r="D60" s="233"/>
-      <c r="E60" s="233"/>
-      <c r="F60" s="233"/>
-      <c r="G60" s="233"/>
-      <c r="H60" s="233"/>
-      <c r="I60" s="233"/>
+      <c r="C60" s="212"/>
+      <c r="D60" s="212"/>
+      <c r="E60" s="212"/>
+      <c r="F60" s="212"/>
+      <c r="G60" s="212"/>
+      <c r="H60" s="212"/>
+      <c r="I60" s="212"/>
       <c r="J60" s="144"/>
       <c r="K60" s="172"/>
       <c r="L60" s="170"/>
@@ -44619,13 +44622,13 @@
     </row>
     <row r="61" spans="2:13" ht="15.6">
       <c r="B61" s="143"/>
-      <c r="C61" s="234"/>
-      <c r="D61" s="234"/>
-      <c r="E61" s="234"/>
-      <c r="F61" s="234"/>
-      <c r="G61" s="234"/>
-      <c r="H61" s="234"/>
-      <c r="I61" s="234"/>
+      <c r="C61" s="213"/>
+      <c r="D61" s="213"/>
+      <c r="E61" s="213"/>
+      <c r="F61" s="213"/>
+      <c r="G61" s="213"/>
+      <c r="H61" s="213"/>
+      <c r="I61" s="213"/>
       <c r="J61" s="144"/>
       <c r="K61" s="172"/>
       <c r="L61" s="170"/>
@@ -44646,41 +44649,41 @@
       <c r="M62" s="175"/>
     </row>
     <row r="63" spans="2:13" ht="15.6">
-      <c r="B63" s="213" t="s">
+      <c r="B63" s="208" t="s">
         <v>127</v>
       </c>
-      <c r="C63" s="200"/>
-      <c r="D63" s="200"/>
-      <c r="E63" s="214"/>
-      <c r="F63" s="199" t="s">
+      <c r="C63" s="209"/>
+      <c r="D63" s="209"/>
+      <c r="E63" s="210"/>
+      <c r="F63" s="234" t="s">
         <v>128</v>
       </c>
-      <c r="G63" s="214"/>
-      <c r="H63" s="199" t="s">
+      <c r="G63" s="210"/>
+      <c r="H63" s="234" t="s">
         <v>129</v>
       </c>
-      <c r="I63" s="200"/>
-      <c r="J63" s="214"/>
+      <c r="I63" s="209"/>
+      <c r="J63" s="210"/>
       <c r="K63" s="173"/>
       <c r="L63" s="145"/>
       <c r="M63" s="146"/>
     </row>
     <row r="64" spans="2:13" ht="15.6" customHeight="1">
-      <c r="B64" s="215" t="s">
+      <c r="B64" s="254" t="s">
         <v>130</v>
       </c>
-      <c r="C64" s="216"/>
-      <c r="D64" s="216"/>
-      <c r="E64" s="216"/>
-      <c r="F64" s="217" t="s">
+      <c r="C64" s="255"/>
+      <c r="D64" s="255"/>
+      <c r="E64" s="255"/>
+      <c r="F64" s="256" t="s">
         <v>131</v>
       </c>
-      <c r="G64" s="218"/>
-      <c r="H64" s="219" t="s">
+      <c r="G64" s="257"/>
+      <c r="H64" s="258" t="s">
         <v>132</v>
       </c>
-      <c r="I64" s="220"/>
-      <c r="J64" s="221"/>
+      <c r="I64" s="259"/>
+      <c r="J64" s="260"/>
       <c r="K64" s="151"/>
       <c r="L64" s="145"/>
       <c r="M64" s="146"/>
@@ -44692,27 +44695,27 @@
       <c r="E65" s="80"/>
       <c r="F65" s="150"/>
       <c r="G65" s="145"/>
-      <c r="H65" s="190"/>
-      <c r="I65" s="191"/>
-      <c r="J65" s="222"/>
+      <c r="H65" s="245"/>
+      <c r="I65" s="246"/>
+      <c r="J65" s="261"/>
       <c r="K65" s="151"/>
       <c r="L65" s="171"/>
       <c r="M65" s="146"/>
     </row>
     <row r="66" spans="2:13" ht="15.6" customHeight="1">
-      <c r="B66" s="197" t="s">
+      <c r="B66" s="252" t="s">
         <v>133</v>
       </c>
-      <c r="C66" s="198"/>
-      <c r="D66" s="198"/>
-      <c r="E66" s="198"/>
-      <c r="F66" s="195" t="s">
+      <c r="C66" s="253"/>
+      <c r="D66" s="253"/>
+      <c r="E66" s="253"/>
+      <c r="F66" s="250" t="s">
         <v>134</v>
       </c>
-      <c r="G66" s="196"/>
-      <c r="H66" s="190"/>
-      <c r="I66" s="191"/>
-      <c r="J66" s="222"/>
+      <c r="G66" s="251"/>
+      <c r="H66" s="245"/>
+      <c r="I66" s="246"/>
+      <c r="J66" s="261"/>
       <c r="K66" s="151"/>
       <c r="L66" s="145"/>
       <c r="M66" s="146"/>
@@ -44724,27 +44727,27 @@
       <c r="E67" s="145"/>
       <c r="F67" s="148"/>
       <c r="G67" s="145"/>
-      <c r="H67" s="190"/>
-      <c r="I67" s="191"/>
-      <c r="J67" s="222"/>
+      <c r="H67" s="245"/>
+      <c r="I67" s="246"/>
+      <c r="J67" s="261"/>
       <c r="K67" s="151"/>
       <c r="L67" s="170"/>
       <c r="M67" s="76"/>
     </row>
     <row r="68" spans="2:13" ht="15.6" customHeight="1">
-      <c r="B68" s="197" t="s">
+      <c r="B68" s="252" t="s">
         <v>135</v>
       </c>
-      <c r="C68" s="198"/>
-      <c r="D68" s="198"/>
-      <c r="E68" s="198"/>
-      <c r="F68" s="195" t="s">
+      <c r="C68" s="253"/>
+      <c r="D68" s="253"/>
+      <c r="E68" s="253"/>
+      <c r="F68" s="250" t="s">
         <v>136</v>
       </c>
-      <c r="G68" s="196"/>
-      <c r="H68" s="190"/>
-      <c r="I68" s="191"/>
-      <c r="J68" s="222"/>
+      <c r="G68" s="251"/>
+      <c r="H68" s="245"/>
+      <c r="I68" s="246"/>
+      <c r="J68" s="261"/>
       <c r="K68" s="151"/>
       <c r="L68" s="170"/>
       <c r="M68" s="76"/>
@@ -44756,30 +44759,30 @@
       <c r="E69" s="80"/>
       <c r="F69" s="150"/>
       <c r="G69" s="153"/>
-      <c r="H69" s="190"/>
-      <c r="I69" s="191"/>
-      <c r="J69" s="222"/>
-      <c r="K69" s="190"/>
-      <c r="L69" s="191"/>
-      <c r="M69" s="192"/>
+      <c r="H69" s="245"/>
+      <c r="I69" s="246"/>
+      <c r="J69" s="261"/>
+      <c r="K69" s="245"/>
+      <c r="L69" s="246"/>
+      <c r="M69" s="247"/>
     </row>
     <row r="70" spans="2:13" ht="15.6" customHeight="1">
-      <c r="B70" s="197" t="s">
+      <c r="B70" s="252" t="s">
         <v>137</v>
       </c>
-      <c r="C70" s="198"/>
-      <c r="D70" s="198"/>
-      <c r="E70" s="198"/>
-      <c r="F70" s="195" t="s">
+      <c r="C70" s="253"/>
+      <c r="D70" s="253"/>
+      <c r="E70" s="253"/>
+      <c r="F70" s="250" t="s">
         <v>138</v>
       </c>
-      <c r="G70" s="196"/>
-      <c r="H70" s="190"/>
-      <c r="I70" s="191"/>
-      <c r="J70" s="222"/>
-      <c r="K70" s="190"/>
-      <c r="L70" s="191"/>
-      <c r="M70" s="192"/>
+      <c r="G70" s="251"/>
+      <c r="H70" s="245"/>
+      <c r="I70" s="246"/>
+      <c r="J70" s="261"/>
+      <c r="K70" s="245"/>
+      <c r="L70" s="246"/>
+      <c r="M70" s="247"/>
     </row>
     <row r="71" spans="2:13" ht="16.2" customHeight="1" thickBot="1">
       <c r="B71" s="154"/>
@@ -44788,9 +44791,9 @@
       <c r="E71" s="155"/>
       <c r="F71" s="156"/>
       <c r="G71" s="157"/>
-      <c r="H71" s="223"/>
-      <c r="I71" s="224"/>
-      <c r="J71" s="225"/>
+      <c r="H71" s="262"/>
+      <c r="I71" s="263"/>
+      <c r="J71" s="264"/>
       <c r="K71" s="158"/>
       <c r="L71" s="157"/>
       <c r="M71" s="159"/>
@@ -44803,26 +44806,6 @@
     </row>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="B1:M1"/>
-    <mergeCell ref="B2:I3"/>
-    <mergeCell ref="J2:M6"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="G10:J10"/>
-    <mergeCell ref="C51:I61"/>
-    <mergeCell ref="K50:M50"/>
-    <mergeCell ref="K49:M49"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="B23:E23"/>
-    <mergeCell ref="J23:M23"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="C24:I25"/>
-    <mergeCell ref="J24:M24"/>
-    <mergeCell ref="K10:M10"/>
-    <mergeCell ref="K11:L11"/>
-    <mergeCell ref="K57:M57"/>
-    <mergeCell ref="K58:M58"/>
-    <mergeCell ref="K51:M51"/>
     <mergeCell ref="K70:M70"/>
     <mergeCell ref="K69:M69"/>
     <mergeCell ref="K25:L25"/>
@@ -44839,6 +44822,26 @@
     <mergeCell ref="F66:G66"/>
     <mergeCell ref="B68:E68"/>
     <mergeCell ref="B49:J50"/>
+    <mergeCell ref="C51:I61"/>
+    <mergeCell ref="K50:M50"/>
+    <mergeCell ref="K49:M49"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="B23:E23"/>
+    <mergeCell ref="J23:M23"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="C24:I25"/>
+    <mergeCell ref="J24:M24"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="K57:M57"/>
+    <mergeCell ref="K58:M58"/>
+    <mergeCell ref="K51:M51"/>
+    <mergeCell ref="B1:M1"/>
+    <mergeCell ref="B2:I3"/>
+    <mergeCell ref="J2:M6"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="G10:J10"/>
+    <mergeCell ref="K10:M10"/>
   </mergeCells>
   <conditionalFormatting sqref="B26:I48">
     <cfRule type="expression" dxfId="3" priority="1">
